--- a/planner/ict257-study-planner.xlsx
+++ b/planner/ict257-study-planner.xlsx
@@ -3136,11 +3136,11 @@
       </c>
       <c r="C6" s="30" t="inlineStr">
         <is>
-          <t>week 3</t>
+          <t>week 4</t>
         </is>
       </c>
       <c r="D6" s="22">
-        <f>SemesterStart+7*(3-1)</f>
+        <f>SemesterStart+7*(4-1)</f>
         <v/>
       </c>
       <c r="E6" s="19" t="inlineStr">

--- a/planner/ict257-study-planner.xlsx
+++ b/planner/ict257-study-planner.xlsx
@@ -1213,7 +1213,7 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>Getting oriented, the command-line assistant and the shell</t>
+          <t>Getting oriented, system documentation, the command-line assistant and the shell</t>
         </is>
       </c>
       <c r="F5" s="22">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>Getting oriented, the command-line assistant and the shell</t>
+          <t>Getting oriented, system documentation, the command-line assistant and the shell</t>
         </is>
       </c>
       <c r="F6" s="22">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>Getting oriented, the command-line assistant and the shell</t>
+          <t>Getting oriented, system documentation, the command-line assistant and the shell</t>
         </is>
       </c>
       <c r="F7" s="22">
@@ -1343,11 +1343,11 @@
         </is>
       </c>
       <c r="D8" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>Manual pages, registering systems, the file-system hierarchy and working with files</t>
+          <t>Getting oriented, system documentation, the command-line assistant and the shell</t>
         </is>
       </c>
       <c r="F8" s="22">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>Manual pages, registering systems, the file-system hierarchy and working with files</t>
+          <t>Registering systems, the file-system hierarchy and working with files</t>
         </is>
       </c>
       <c r="F9" s="22">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>Getting oriented, the command-line assistant and the shell</t>
+          <t>Getting oriented, system documentation, the command-line assistant and the shell</t>
         </is>
       </c>
       <c r="F10" s="22">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E11" s="21" t="inlineStr">
         <is>
-          <t>Manual pages, registering systems, the file-system hierarchy and working with files</t>
+          <t>Registering systems, the file-system hierarchy and working with files</t>
         </is>
       </c>
       <c r="F11" s="22">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>Manual pages, registering systems, the file-system hierarchy and working with files</t>
+          <t>Registering systems, the file-system hierarchy and working with files</t>
         </is>
       </c>
       <c r="F12" s="22">
